--- a/SCH-STH/Impact assessments/Senegal/2025/mai/sn_sch_sth_impact_202505_1_site_v2.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/mai/sn_sch_sth_impact_202505_1_site_v2.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TFGH-WHO-Sightsavers\SENEGAL\Evaluation d'Impact SCH-STH Senegal Mai 2025\Forms\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\mai\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA43149F-C2BF-4355-AE9A-1DA06E49D0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="498" activeTab="1"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -17,16 +18,6 @@
     <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -2291,7 +2282,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -2633,10 +2624,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Excel Built-in Normal" xfId="1"/>
+    <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 3" xfId="3"/>
-    <cellStyle name="Normal 3 2" xfId="2"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 3 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2976,7 +2967,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R46"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4155,7 +4146,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H950"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18797,7 +18788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
